--- a/SGC-CKN/Excel/75eb6561-34b6-401c-a353-18a2107045a5_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-07_D800_13-03-2026.xlsx
+++ b/SGC-CKN/Excel/75eb6561-34b6-401c-a353-18a2107045a5_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-07_D800_13-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="62">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P7-07</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>KCL-0002</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">08:30
@@ -106,13 +106,10 @@
 13/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">10:48
@@ -122,9 +119,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">11:33
 13/03/2026</t>
   </si>
@@ -142,7 +136,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:00
@@ -152,9 +146,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">14:30
 13/03/2026</t>
   </si>
@@ -162,7 +153,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">15:48
@@ -175,7 +166,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1. Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">16:40
@@ -183,9 +174,6 @@
   </si>
   <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">20:23
@@ -226,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -297,11 +285,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF831843"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
@@ -320,7 +303,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -390,11 +373,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBCFE8"/>
       </patternFill>
     </fill>
     <fill>
@@ -495,7 +473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -590,22 +568,13 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1206,24 +1175,24 @@
         <v>7.6</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="9">
         <v>-8.31</v>
@@ -1241,24 +1210,24 @@
         <v>1.81</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F13" s="13">
         <v>-10.81</v>
@@ -1276,24 +1245,24 @@
         <v>10.8</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F14" s="16">
         <v>-18.91</v>
@@ -1311,24 +1280,24 @@
         <v>2.87</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F15" s="19">
         <v>-23.31</v>
@@ -1346,163 +1315,163 @@
         <v>4.36</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="22" t="s">
+      <c r="A16" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="24" t="s">
+      <c r="C16" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="22">
+      <c r="F16" s="19">
         <v>-27.31</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="19">
         <v>-36.81</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="19">
         <v>0.5</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="19">
         <v>9.5</v>
       </c>
       <c r="J16" s="8">
         <v>19</v>
       </c>
-      <c r="K16" s="23" t="s">
-        <v>30</v>
+      <c r="K16" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="25" t="s">
+      <c r="A17" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="27" t="s">
+      <c r="C17" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="F17" s="22">
         <v>-36.81</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="22">
         <v>-39.81</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="22">
         <v>1.3</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="22">
         <v>3</v>
       </c>
       <c r="J17" s="12">
         <v>2.31</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="27" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="28">
+      <c r="F18" s="25">
         <v>-39.81</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="25">
         <v>-41.81</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="25">
         <v>0.87</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="25">
         <v>2</v>
       </c>
       <c r="J18" s="12">
         <v>2.31</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K18" s="26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="30" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="33" t="s">
+      <c r="E19" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" s="28">
+        <v>-41.81</v>
+      </c>
+      <c r="G19" s="28">
+        <v>-44.95</v>
+      </c>
+      <c r="H19" s="28">
+        <v>3.72</v>
+      </c>
+      <c r="I19" s="28">
+        <v>3.14</v>
+      </c>
+      <c r="J19" s="31">
+        <v>0.84</v>
+      </c>
+      <c r="K19" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="31">
-        <v>-41.81</v>
-      </c>
-      <c r="G19" s="31">
-        <v>-44.95</v>
-      </c>
-      <c r="H19" s="31">
-        <v>3.72</v>
-      </c>
-      <c r="I19" s="31">
-        <v>3.14</v>
-      </c>
-      <c r="J19" s="34">
-        <v>0.84</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
     </row>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1584,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1597,31 +1566,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1661,7 +1630,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1690,7 +1659,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1719,7 +1688,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1748,25 +1717,25 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="19">
         <v>-23.31</v>
       </c>
       <c r="F6" s="19">
-        <v>-27.31</v>
+        <v>-36.81</v>
       </c>
       <c r="G6" s="19">
-        <v>0.92</v>
+        <v>1.42</v>
       </c>
       <c r="H6" s="19">
-        <v>4</v>
-      </c>
-      <c r="I6" s="12">
-        <v>4.36</v>
+        <v>13.5</v>
+      </c>
+      <c r="I6" s="8">
+        <v>9.53</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1783,19 +1752,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-27.31</v>
+        <v>-36.81</v>
       </c>
       <c r="F7" s="22">
-        <v>-36.81</v>
+        <v>-39.81</v>
       </c>
       <c r="G7" s="22">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="H7" s="22">
-        <v>9.5</v>
-      </c>
-      <c r="I7" s="8">
-        <v>19</v>
+        <v>3</v>
+      </c>
+      <c r="I7" s="12">
+        <v>2.31</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1806,22 +1775,22 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-36.81</v>
+        <v>-39.81</v>
       </c>
       <c r="F8" s="25">
-        <v>-39.81</v>
+        <v>-41.81</v>
       </c>
       <c r="G8" s="25">
-        <v>1.3</v>
+        <v>0.87</v>
       </c>
       <c r="H8" s="25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" s="12">
         <v>2.31</v>
@@ -1835,82 +1804,53 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-39.81</v>
+        <v>-41.81</v>
       </c>
       <c r="F9" s="28">
-        <v>-41.81</v>
+        <v>-44.95</v>
       </c>
       <c r="G9" s="28">
-        <v>0.87</v>
+        <v>3.72</v>
       </c>
       <c r="H9" s="28">
-        <v>2</v>
-      </c>
-      <c r="I9" s="12">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="31">
+        <v>3.14</v>
+      </c>
+      <c r="I9" s="31">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="31">
-        <v>1</v>
-      </c>
-      <c r="E10" s="31">
-        <v>-41.81</v>
-      </c>
-      <c r="F10" s="31">
+      <c r="C10" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="34">
+        <v>9</v>
+      </c>
+      <c r="E10" s="34">
+        <v>-1.34</v>
+      </c>
+      <c r="F10" s="34">
         <v>-44.95</v>
       </c>
-      <c r="G10" s="31">
-        <v>3.72</v>
-      </c>
-      <c r="H10" s="31">
-        <v>3.14</v>
+      <c r="G10" s="34">
+        <v>11.88</v>
+      </c>
+      <c r="H10" s="34">
+        <v>43.61</v>
       </c>
       <c r="I10" s="34">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="37">
-        <v>9</v>
-      </c>
-      <c r="E11" s="37">
-        <v>-1.34</v>
-      </c>
-      <c r="F11" s="37">
-        <v>-44.95</v>
-      </c>
-      <c r="G11" s="37">
-        <v>11.88</v>
-      </c>
-      <c r="H11" s="37">
-        <v>43.61</v>
-      </c>
-      <c r="I11" s="37">
         <v>3.67</v>
       </c>
     </row>

--- a/SGC-CKN/Excel/75eb6561-34b6-401c-a353-18a2107045a5_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-07_D800_13-03-2026.xlsx
+++ b/SGC-CKN/Excel/75eb6561-34b6-401c-a353-18a2107045a5_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-07_D800_13-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="63">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGC-KCN0001</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -104,6 +104,9 @@
   <si>
     <t xml:space="preserve">09:25
 13/03/2026</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>2</t>
@@ -1175,24 +1178,24 @@
         <v>7.6</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-8.31</v>
@@ -1210,12 +1213,12 @@
         <v>1.81</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
@@ -1224,10 +1227,10 @@
         <v>27</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F13" s="13">
         <v>-10.81</v>
@@ -1245,24 +1248,24 @@
         <v>10.8</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" s="16">
         <v>-18.91</v>
@@ -1280,24 +1283,24 @@
         <v>2.87</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F15" s="19">
         <v>-23.31</v>
@@ -1315,24 +1318,24 @@
         <v>4.36</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" s="19">
         <v>-27.31</v>
@@ -1350,24 +1353,24 @@
         <v>19</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F17" s="22">
         <v>-36.81</v>
@@ -1385,24 +1388,24 @@
         <v>2.31</v>
       </c>
       <c r="K17" s="23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F18" s="25">
         <v>-39.81</v>
@@ -1420,24 +1423,24 @@
         <v>2.31</v>
       </c>
       <c r="K18" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F19" s="28">
         <v>-41.81</v>
@@ -1455,12 +1458,12 @@
         <v>0.84</v>
       </c>
       <c r="K19" s="29" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="32"/>
@@ -1566,31 +1569,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1630,7 +1633,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1688,7 +1691,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1717,7 +1720,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="19">
         <v>2</v>
@@ -1746,7 +1749,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1775,7 +1778,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1804,7 +1807,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1827,13 +1830,13 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D10" s="34">
         <v>9</v>
